--- a/04_DESIGN_TABLES/DesignTable_2605_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2605_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -946,12 +946,17 @@
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
           <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=0.88~0.875; D_1@BORE=0.39~0.391; D1@BORE=0.53~0.531; D3@BORE=0.39~0.391</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1163,12 +1168,17 @@
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
           <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=0.56~0.562; D_1@BORE=0.17~0.172; D1@BORE=0.28~0.281; D3@BORE=0.17~0.172</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1380,7 +1390,7 @@
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -1390,7 +1400,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=0.56~0.562; D_1@BORE=0.3~0.297; D1@BORE=0.28~0.281; D3@BORE=0.3~0.297 | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -1406,7 +1416,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="C5" t="n">
         <v>0.375</v>
@@ -1454,7 +1464,7 @@
         <v>0.1522</v>
       </c>
       <c r="R5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
         <v>0.375</v>
@@ -1487,7 +1497,7 @@
         <v>0.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AD5" t="n">
         <v>0.41</v>
@@ -1499,7 +1509,7 @@
         <v>0.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
         <v>0.5625</v>
@@ -1559,7 +1569,7 @@
         <v>0.75</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.504</v>
+        <v>0.584</v>
       </c>
       <c r="BB5" t="n">
         <v>0.66</v>
@@ -1568,7 +1578,7 @@
         <v>0.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.504</v>
+        <v>0.584</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -1607,7 +1617,12 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree); M1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N837 = 1.140 (table had 1.06) [user 2026-10-18 A19]; M3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P837 = 1.140 (table had 1.06) [user 2026-10-18 A19] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): M1@DRIVE 1.06 -&gt; OMi 1.140 (Items!N837, M186) | A19 (user 2026-10-18, group 3 open): M3@DRIVE 1.06 -&gt; OMi 1.140 (Items!P837, M188)</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -1819,7 +1834,7 @@
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
@@ -1829,7 +1844,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=1.06~1.062; D_1@BORE=0.61~0.609; D1@BORE=0.72~0.719; D3@BORE=0.61~0.609 | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2041,7 +2056,7 @@
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
@@ -2051,7 +2066,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3125 (round end proud of the flats by 0.0067; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=1.31~1.312; D_1@BORE=0.84~0.844; D1@BORE=0.94~0.938; D3@BORE=0.84~0.844 | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3125 (round end proud of the flats by 0.0067; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -2263,7 +2278,7 @@
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -2273,7 +2288,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@HEX=1.63~1.625; D_1@BORE=1.08~1.078; D1@BORE=1.25~1.250; D3@BORE=1.08~1.078 | leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2605_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2605_SW2.xlsx
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="C5" t="n">
         <v>0.375</v>
@@ -1464,7 +1464,7 @@
         <v>0.1522</v>
       </c>
       <c r="R5" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="S5" t="n">
         <v>0.375</v>
@@ -1497,7 +1497,7 @@
         <v>0.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AD5" t="n">
         <v>0.41</v>
@@ -1509,7 +1509,7 @@
         <v>0.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AH5" t="n">
         <v>0.5625</v>
@@ -1569,7 +1569,7 @@
         <v>0.75</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.584</v>
+        <v>0.504</v>
       </c>
       <c r="BB5" t="n">
         <v>0.66</v>
@@ -1578,7 +1578,7 @@
         <v>0.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.584</v>
+        <v>0.504</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree); M1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N837 = 1.140 (table had 1.06) [user 2026-10-18 A19]; M3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P837 = 1.140 (table had 1.06) [user 2026-10-18 A19] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s173 only (double-pass 31 rows); pass1 stated ROWS=32 but enumerated 31; pass2 31; Series sheet n=30 -&gt; 31 accepted (both passes agree); M1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N837 = 1.140 (table had 1.06) [user 2026-10-18 A19]; M3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P837 = 1.140 (table had 1.06) [user 2026-10-18 A19]; M1@DRIVE: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; M3@DRIVE: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): M1@DRIVE 1.06 -&gt; OMi 1.140 (Items!N837, M186) | A19 (user 2026-10-18, group 3 open): M3@DRIVE 1.06 -&gt; OMi 1.140 (Items!P837, M188)</t>
+          <t>A19 (user 2026-10-18, group 3 open): M1@DRIVE 1.06 -&gt; OMi 1.140 (Items!N837, M186) | A19 (user 2026-10-18, group 3 open): M3@DRIVE 1.06 -&gt; OMi 1.140 (Items!P837, M188) | 2026-10-20 Air-Way first: M1@DRIVE OMi/Brennan 1.14 -&gt; Air-Way 1.06 | 2026-10-20 Air-Way first: M3@DRIVE OMi/Brennan 1.14 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
